--- a/LAN_Network_Devices.xlsx
+++ b/LAN_Network_Devices.xlsx
@@ -81,7 +81,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="50">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -92,6 +99,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -106,6 +127,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -113,6 +155,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -120,6 +176,27 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -127,6 +204,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -148,6 +232,104 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.5998718222602009"/>
         </patternFill>
       </fill>
@@ -155,13 +337,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.7998901333658864"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4" tint="0.5998718222602009"/>
         </patternFill>
       </fill>
@@ -172,6 +347,108 @@
           <bgColor theme="4" tint="0.7998901333658864"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -233,6 +510,24 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -332,18 +627,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1_2" displayName="Table1_2" ref="A1:I6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="17">
-  <autoFilter ref="A1:I6"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1_2" displayName="Table1_2" ref="A1:N8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="49">
+  <autoFilter ref="A1:N8"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="Hostname"/>
     <tableColumn id="2" name="Model"/>
     <tableColumn id="3" name="OOBM IP Address"/>
     <tableColumn id="4" name="Current IOS Version"/>
     <tableColumn id="5" name="Recommended IOS Version"/>
-    <tableColumn id="6" name="Status" dataDxfId="16"/>
-    <tableColumn id="7" name="Enough Flash Space" dataDxfId="15"/>
-    <tableColumn id="9" name="Update IOS File Present" dataDxfId="14"/>
-    <tableColumn id="8" name="Needs Update" dataDxfId="13"/>
+    <tableColumn id="6" name="Status" dataDxfId="48"/>
+    <tableColumn id="10" name="Auth Status" dataDxfId="47"/>
+    <tableColumn id="7" name="Enough Flash Space" dataDxfId="46"/>
+    <tableColumn id="9" name="Update IOS File Present" dataDxfId="45"/>
+    <tableColumn id="8" name="Needs Update" dataDxfId="44"/>
+    <tableColumn id="12" name="Transfer Result" dataDxfId="43"/>
+    <tableColumn id="11" name="Install Status" dataDxfId="42"/>
+    <tableColumn id="13" name="Update Result" dataDxfId="41"/>
+    <tableColumn id="14" name="Cleaned Inactive" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -529,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="14.140625" customWidth="1" min="1" max="1"/>
@@ -538,9 +838,14 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="10.42578125" customWidth="1" min="6" max="6"/>
-    <col width="21.5703125" customWidth="1" min="7" max="7"/>
-    <col width="25.42578125" customWidth="1" min="8" max="8"/>
-    <col width="16.28515625" customWidth="1" min="9" max="9"/>
+    <col width="13.5703125" customWidth="1" min="7" max="7"/>
+    <col width="21.5703125" customWidth="1" min="8" max="8"/>
+    <col width="25.42578125" customWidth="1" min="9" max="9"/>
+    <col width="16.28515625" customWidth="1" min="10" max="10"/>
+    <col width="18.140625" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17.5703125" customWidth="1" min="13" max="13"/>
+    <col width="19.28515625" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -576,17 +881,42 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Auth Status</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Enough Flash Space</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Update IOS File Present</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Needs Update</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Transfer Result</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Install Status</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Update Result</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Cleaned Inactive</t>
         </is>
       </c>
     </row>
@@ -623,17 +953,42 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
+          <t>AUTH_OK</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -670,7 +1025,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AUTH_OK</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -680,34 +1035,59 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="4" ht="13.9" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>SW3</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>C8KV</t>
+          <t>C9200</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>10.17.1.11</t>
+          <t>10.17.1.15</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>17.13.1a</t>
+          <t>17.12.6</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>17.15.04c</t>
+          <t>17.12.05</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -717,44 +1097,69 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
+          <t>AUTH_OK</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>INSTALL_TRIGGERED</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13.9" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>SW4</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>C8KV</t>
+          <t>C9200</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>10.17.1.12</t>
+          <t>10.17.1.16</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>17.13.1a</t>
+          <t>17.15.4</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>17.15.04c</t>
+          <t>17.15.05</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -764,117 +1169,411 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
+          <t>AUTH_OK</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>INSTALL_TRIGGERED</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13.9" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>C8KV</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>10.17.1.11</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>17.13.1a</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>17.15.04c</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>AUTH_OK</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="13.9" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>C8KV</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>10.17.1.12</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>17.15.04c</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>AUTH_BAD</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="13.9" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>C8KV</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>10.17.1.13</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>17.13.1a</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>17.12.06</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>ONLINE</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>AUTH_OK</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="1048575" ht="12.75" customHeight="1"/>
-    <row r="1048576" ht="12.75" customHeight="1"/>
+    <row r="9" ht="14.25" customHeight="1"/>
   </sheetData>
+  <conditionalFormatting sqref="A4:A5">
+    <cfRule type="expression" priority="38" dxfId="31">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="37" dxfId="30">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:E3">
-    <cfRule type="expression" priority="23" dxfId="12">
+    <cfRule type="expression" priority="61" dxfId="30">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" dxfId="11">
+    <cfRule type="expression" priority="62" dxfId="31">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:E6">
-    <cfRule type="expression" priority="25" dxfId="10">
+  <conditionalFormatting sqref="A6:E8">
+    <cfRule type="expression" priority="64" dxfId="35">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="34">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" priority="26" dxfId="9">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:B5">
+    <cfRule type="expression" priority="36" dxfId="31">
       <formula>ISODD(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="30">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:E5">
+    <cfRule type="expression" priority="34" dxfId="31">
+      <formula>ISODD(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="33" dxfId="30">
+      <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="52" operator="equal" dxfId="1">
+      <formula>"OFFLINE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="51" operator="equal" dxfId="0">
       <formula>"ONLINE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" dxfId="0">
-      <formula>"OFFLINE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="1">
+      <formula>"AUTH_BAD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="0">
+      <formula>"AUTH_OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:I1048576">
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="5">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:I1048576">
+    <cfRule type="cellIs" priority="50" operator="equal" dxfId="0">
+      <formula>"YES"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="49" operator="equal" dxfId="1">
+      <formula>"NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:K1048576">
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="5">
       <formula>"UNKNOWN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:H1048576">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+  <conditionalFormatting sqref="J1:J1048576">
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="1">
+      <formula>"YES"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="39" operator="equal" dxfId="0">
+      <formula>"NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="1">
+      <formula>"FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="5">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
-      <formula>"NO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
-      <formula>"YES"</formula>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="0">
+      <formula>"SUCCESS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">
-      <formula>"NO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
-      <formula>"YES"</formula>
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="5">
+      <formula>"NOT_ATTEMPTED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
+      <formula>"CONNECT_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+      <formula>"UNEXPECTED_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
+      <formula>"ADD_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+      <formula>"ACTIVATE_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
+      <formula>"INSTALL_TRIGGERED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="5">
+      <formula>"ABORTED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
+      <formula>"SUCCESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
+      <formula>"FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="5">
+      <formula>"COMMIT_FAILED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:N1048576">
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="5">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
+      <formula>"UNKNOWN"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1:N1048576">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
+      <formula>"CLEANED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"CLEANED_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"CONNECT_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"UNEXPECTED_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"NOTHING_TO_CLEAN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/LAN_Network_Devices.xlsx
+++ b/LAN_Network_Devices.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LAB_NETAUTO001" sheetId="1" state="visible" r:id="rId1"/>
@@ -31,7 +31,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
@@ -72,11 +78,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -849,17 +856,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Hostname</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>OOBM IP Address</t>
         </is>
@@ -869,7 +876,7 @@
           <t>Current IOS Version</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Recommended IOS Version</t>
         </is>
@@ -936,11 +943,7 @@
           <t>10.17.1.10</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>17.12.1prd9</t>
-        </is>
-      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
           <t>17.12.02prd9</t>
@@ -948,27 +951,27 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>OFFLINE</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>AUTH_OK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>YES</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
@@ -1082,12 +1085,12 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>17.12.6</t>
+          <t>17.12.5</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>17.12.05</t>
+          <t>17.12.06</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -1154,12 +1157,12 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>17.15.4</t>
+          <t>17.15.5</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>17.15.05</t>
+          <t>17.15.04</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
@@ -1224,11 +1227,7 @@
           <t>10.17.1.11</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>17.13.1a</t>
-        </is>
-      </c>
+      <c r="D6" s="1" t="inlineStr"/>
       <c r="E6" s="1" t="inlineStr">
         <is>
           <t>17.15.04c</t>
@@ -1241,22 +1240,22 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>AUTH_OK</t>
+          <t>AUTH_BAD</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
@@ -1296,12 +1295,14 @@
           <t>10.17.1.12</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
-        <v/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>17.13.1a</t>
+        </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>17.15.04c</t>
+          <t>17.15.05c</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
@@ -1311,22 +1312,22 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>AUTH_BAD</t>
+          <t>AUTH_OK</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">

--- a/LAN_Network_Devices.xlsx
+++ b/LAN_Network_Devices.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LAB_NETAUTO001" sheetId="1" state="visible" r:id="rId1"/>
@@ -78,224 +78,230 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+  <dxfs count="105">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
         </patternFill>
       </fill>
     </dxf>
@@ -323,6 +329,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="5" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="4" tint="0.5998718222602009"/>
         </patternFill>
       </fill>
@@ -330,6 +350,363 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.7998901333658864"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.5998718222602009"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.7998901333658864"/>
         </patternFill>
       </fill>
@@ -368,6 +745,34 @@
           <bgColor theme="4" tint="0.5998718222602009"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -554,11 +959,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -634,7 +1034,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1_2" displayName="Table1_2" ref="A1:N8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1_2" displayName="Table1_2" ref="A1:N8" headerRowCount="1" totalsRowShown="0" headerRowDxfId="94" headerRowBorderDxfId="95">
   <autoFilter ref="A1:N8"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Hostname"/>
@@ -642,15 +1042,15 @@
     <tableColumn id="3" name="OOBM IP Address"/>
     <tableColumn id="4" name="Current IOS Version"/>
     <tableColumn id="5" name="Recommended IOS Version"/>
-    <tableColumn id="6" name="Status" dataDxfId="48"/>
-    <tableColumn id="10" name="Auth Status" dataDxfId="47"/>
-    <tableColumn id="7" name="Enough Flash Space" dataDxfId="46"/>
-    <tableColumn id="9" name="Update IOS File Present" dataDxfId="45"/>
-    <tableColumn id="8" name="Needs Update" dataDxfId="44"/>
-    <tableColumn id="12" name="Transfer Result" dataDxfId="43"/>
-    <tableColumn id="11" name="Install Status" dataDxfId="42"/>
-    <tableColumn id="13" name="Update Result" dataDxfId="41"/>
-    <tableColumn id="14" name="Cleaned Inactive" dataDxfId="40"/>
+    <tableColumn id="6" name="Status" dataDxfId="104"/>
+    <tableColumn id="10" name="Auth Status" dataDxfId="103"/>
+    <tableColumn id="7" name="Enough Flash Space" dataDxfId="102"/>
+    <tableColumn id="9" name="Update IOS File Present" dataDxfId="101"/>
+    <tableColumn id="8" name="Needs Update" dataDxfId="100"/>
+    <tableColumn id="12" name="Transfer Result" dataDxfId="99"/>
+    <tableColumn id="11" name="Install Status" dataDxfId="98"/>
+    <tableColumn id="13" name="Update Result" dataDxfId="97"/>
+    <tableColumn id="14" name="Cleaned Inactive" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -856,17 +1256,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Hostname</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>OOBM IP Address</t>
         </is>
@@ -876,7 +1276,7 @@
           <t>Current IOS Version</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Recommended IOS Version</t>
         </is>
@@ -896,32 +1296,32 @@
           <t>Enough Flash Space</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Update IOS File Present</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Needs Update</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Transfer Result</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Install Status</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Update Result</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Cleaned Inactive</t>
         </is>
@@ -974,26 +1374,10 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>NOT_ATTEMPTED</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K2" s="1" t="inlineStr"/>
+      <c r="L2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr"/>
+      <c r="N2" s="1" t="inlineStr"/>
     </row>
     <row r="3" ht="13.9" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -1046,26 +1430,10 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>NOT_ATTEMPTED</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K3" s="1" t="inlineStr"/>
+      <c r="L3" s="1" t="inlineStr"/>
+      <c r="M3" s="1" t="inlineStr"/>
+      <c r="N3" s="1" t="inlineStr"/>
     </row>
     <row r="4" ht="13.9" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -1083,11 +1451,7 @@
           <t>10.17.1.15</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>17.12.5</t>
-        </is>
-      </c>
+      <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr">
         <is>
           <t>17.12.06</t>
@@ -1105,39 +1469,23 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>INSTALL_TRIGGERED</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="inlineStr">
-        <is>
-          <t>CLEANED</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
+      <c r="L4" s="1" t="inlineStr"/>
+      <c r="M4" s="1" t="inlineStr"/>
+      <c r="N4" s="1" t="inlineStr"/>
     </row>
     <row r="5" ht="13.9" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -1190,26 +1538,10 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>INSTALL_TRIGGERED</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>CLEANED</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
+      <c r="L5" s="1" t="inlineStr"/>
+      <c r="M5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr"/>
     </row>
     <row r="6" ht="13.9" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -1258,26 +1590,10 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="1" t="inlineStr">
-        <is>
-          <t>NOT_ATTEMPTED</t>
-        </is>
-      </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
+      <c r="L6" s="1" t="inlineStr"/>
+      <c r="M6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr"/>
     </row>
     <row r="7" ht="13.9" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -1330,26 +1646,10 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>NOT_ATTEMPTED</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr"/>
+      <c r="M7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr"/>
     </row>
     <row r="8" ht="13.9" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -1402,179 +1702,163 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="1" t="inlineStr">
-        <is>
-          <t>NOT_ATTEMPTED</t>
-        </is>
-      </c>
-      <c r="M8" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
+      <c r="L8" s="1" t="inlineStr"/>
+      <c r="M8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr"/>
     </row>
     <row r="9" ht="14.25" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A4:A5">
-    <cfRule type="expression" priority="38" dxfId="31">
+    <cfRule type="expression" priority="44" dxfId="31">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="30">
       <formula>ISODD(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" priority="37" dxfId="30">
-      <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:E3">
-    <cfRule type="expression" priority="61" dxfId="30">
+    <cfRule type="expression" priority="68" dxfId="31">
       <formula>ISEVEN(ROW())</formula>
     </cfRule>
-    <cfRule type="expression" priority="62" dxfId="31">
+    <cfRule type="expression" priority="69" dxfId="30">
       <formula>ISODD(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:E8">
-    <cfRule type="expression" priority="64" dxfId="35">
+    <cfRule type="expression" priority="70" dxfId="35">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="71" dxfId="34">
       <formula>ISODD(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" priority="63" dxfId="34">
-      <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B5">
-    <cfRule type="expression" priority="36" dxfId="31">
+    <cfRule type="expression" priority="42" dxfId="31">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="43" dxfId="30">
       <formula>ISODD(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" priority="35" dxfId="30">
-      <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E5">
-    <cfRule type="expression" priority="34" dxfId="31">
+    <cfRule type="expression" priority="40" dxfId="31">
+      <formula>ISEVEN(ROW())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="41" dxfId="30">
       <formula>ISODD(ROW())</formula>
-    </cfRule>
-    <cfRule type="expression" priority="33" dxfId="30">
-      <formula>ISEVEN(ROW())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="cellIs" priority="52" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="58" operator="equal" dxfId="0">
+      <formula>"ONLINE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="59" operator="equal" dxfId="1">
       <formula>"OFFLINE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="51" operator="equal" dxfId="0">
-      <formula>"ONLINE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" priority="31" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="0">
+      <formula>"AUTH_OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="1">
       <formula>"AUTH_BAD"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="30" operator="equal" dxfId="0">
-      <formula>"AUTH_OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:I1048576">
-    <cfRule type="cellIs" priority="29" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="5">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1048576">
-    <cfRule type="cellIs" priority="50" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="56" operator="equal" dxfId="1">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="57" operator="equal" dxfId="0">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="49" operator="equal" dxfId="1">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:K1048576">
-    <cfRule type="cellIs" priority="25" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="5">
       <formula>"UNKNOWN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="cellIs" priority="40" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="0">
+      <formula>"NO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="47" operator="equal" dxfId="1">
       <formula>"YES"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="39" operator="equal" dxfId="0">
-      <formula>"NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K1048576">
-    <cfRule type="cellIs" priority="28" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="5">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="34" operator="equal" dxfId="0">
+      <formula>"SUCCESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="35" operator="equal" dxfId="1">
       <formula>"FAILED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="24" operator="equal" dxfId="5">
-      <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="27" operator="equal" dxfId="0">
-      <formula>"SUCCESS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="cellIs" priority="20" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
+      <formula>"ACTIVATE_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
+      <formula>"ADD_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="1">
+      <formula>"UNEXPECTED_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="1">
+      <formula>"CONNECT_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="5">
       <formula>"NOT_ATTEMPTED"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="19" operator="equal" dxfId="1">
-      <formula>"CONNECT_ERROR"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="equal" dxfId="1">
-      <formula>"UNEXPECTED_ERROR"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" dxfId="1">
-      <formula>"ADD_FAILED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
-      <formula>"ACTIVATE_FAILED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="5">
+      <formula>"ABORTED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="0">
       <formula>"INSTALL_TRIGGERED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="21" operator="equal" dxfId="5">
-      <formula>"ABORTED"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="5">
+      <formula>"COMMIT_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="1">
+      <formula>"FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"SUCCESS"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
-      <formula>"FAILED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" dxfId="5">
-      <formula>"COMMIT_FAILED"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:N1048576">
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="5">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="5">
+      <formula>"UNKNOWN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="5">
       <formula>"N/A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
-      <formula>"UNKNOWN"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
     <cfRule type="cellIs" priority="8" operator="equal" dxfId="0">
+      <formula>"NOTHING_TO_CLEAN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="1">
+      <formula>"UNEXPECTED_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="1">
+      <formula>"CONNECT_ERROR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+      <formula>"CLEANED_FAILED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="0">
       <formula>"CLEANED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
-      <formula>"CLEANED_FAILED"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
-      <formula>"CONNECT_ERROR"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"UNEXPECTED_ERROR"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"NOTHING_TO_CLEAN"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/LAN_Network_Devices.xlsx
+++ b/LAN_Network_Devices.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LAB_NETAUTO001" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LAB_NETAUTO001" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -1374,10 +1374,26 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
-      <c r="N2" s="1" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="13.9" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -1430,10 +1446,26 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr"/>
-      <c r="L3" s="1" t="inlineStr"/>
-      <c r="M3" s="1" t="inlineStr"/>
-      <c r="N3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="13.9" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -1451,7 +1483,11 @@
           <t>10.17.1.15</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>17.12.5</t>
+        </is>
+      </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
           <t>17.12.06</t>
@@ -1469,23 +1505,39 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr"/>
-      <c r="L4" s="1" t="inlineStr"/>
-      <c r="M4" s="1" t="inlineStr"/>
-      <c r="N4" s="1" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>INSTALL_TRIGGERED</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="13.9" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -1538,10 +1590,26 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr"/>
-      <c r="L5" s="1" t="inlineStr"/>
-      <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>INSTALL_TRIGGERED</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>CLEANED</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="13.9" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -1590,10 +1658,26 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr"/>
-      <c r="L6" s="1" t="inlineStr"/>
-      <c r="M6" s="1" t="inlineStr"/>
-      <c r="N6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="13.9" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -1646,10 +1730,26 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-      <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="13.9" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -1702,10 +1802,26 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr"/>
-      <c r="L8" s="1" t="inlineStr"/>
-      <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>NOT_ATTEMPTED</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="14.25" customHeight="1"/>
   </sheetData>
